--- a/outputs/gebaeudemodell/raw/GebTyp_funktion/gebaeudetypen_auswertung_kumuliert_GebTyp_funktion.xlsx
+++ b/outputs/gebaeudemodell/raw/GebTyp_funktion/gebaeudetypen_auswertung_kumuliert_GebTyp_funktion.xlsx
@@ -499,16 +499,16 @@
         <v>131504598</v>
       </c>
       <c r="F2" t="n">
-        <v>131.504598</v>
+        <v>131.5</v>
       </c>
       <c r="G2" t="n">
-        <v>61.45422233856524</v>
+        <v>61.454</v>
       </c>
       <c r="H2" t="n">
-        <v>131.504598</v>
+        <v>131.5</v>
       </c>
       <c r="I2" t="n">
-        <v>61.45422233856524</v>
+        <v>61.454</v>
       </c>
       <c r="J2" t="inlineStr"/>
     </row>
@@ -531,16 +531,16 @@
         <v>26800578</v>
       </c>
       <c r="F3" t="n">
-        <v>26.800578</v>
+        <v>26.8</v>
       </c>
       <c r="G3" t="n">
-        <v>12.52434290711311</v>
+        <v>12.524</v>
       </c>
       <c r="H3" t="n">
-        <v>158.305176</v>
+        <v>158.31</v>
       </c>
       <c r="I3" t="n">
-        <v>73.97856524567837</v>
+        <v>73.979</v>
       </c>
       <c r="J3" t="inlineStr"/>
     </row>
@@ -563,16 +563,16 @@
         <v>7654142</v>
       </c>
       <c r="F4" t="n">
-        <v>7.654142</v>
+        <v>7.65</v>
       </c>
       <c r="G4" t="n">
-        <v>3.576904164818256</v>
+        <v>3.577</v>
       </c>
       <c r="H4" t="n">
-        <v>165.959318</v>
+        <v>165.96</v>
       </c>
       <c r="I4" t="n">
-        <v>77.55546941049661</v>
+        <v>77.55500000000001</v>
       </c>
       <c r="J4" t="inlineStr"/>
     </row>
@@ -595,16 +595,16 @@
         <v>6340192</v>
       </c>
       <c r="F5" t="n">
-        <v>6.340192</v>
+        <v>6.34</v>
       </c>
       <c r="G5" t="n">
-        <v>2.962874110585796</v>
+        <v>2.963</v>
       </c>
       <c r="H5" t="n">
-        <v>172.29951</v>
+        <v>172.3</v>
       </c>
       <c r="I5" t="n">
-        <v>80.51834352108241</v>
+        <v>80.518</v>
       </c>
       <c r="J5" t="inlineStr"/>
     </row>
@@ -627,16 +627,16 @@
         <v>5589098</v>
       </c>
       <c r="F6" t="n">
-        <v>5.589098</v>
+        <v>5.59</v>
       </c>
       <c r="G6" t="n">
-        <v>2.611875754823648</v>
+        <v>2.612</v>
       </c>
       <c r="H6" t="n">
-        <v>177.888608</v>
+        <v>177.89</v>
       </c>
       <c r="I6" t="n">
-        <v>83.13021927590606</v>
+        <v>83.13</v>
       </c>
       <c r="J6" t="inlineStr"/>
     </row>
@@ -659,16 +659,16 @@
         <v>5029282</v>
       </c>
       <c r="F7" t="n">
-        <v>5.029282</v>
+        <v>5.03</v>
       </c>
       <c r="G7" t="n">
-        <v>2.350264697446884</v>
+        <v>2.35</v>
       </c>
       <c r="H7" t="n">
-        <v>182.91789</v>
+        <v>182.92</v>
       </c>
       <c r="I7" t="n">
-        <v>85.48048397335293</v>
+        <v>85.48</v>
       </c>
       <c r="J7" t="inlineStr"/>
     </row>
@@ -691,16 +691,16 @@
         <v>4567457</v>
       </c>
       <c r="F8" t="n">
-        <v>4.567457</v>
+        <v>4.57</v>
       </c>
       <c r="G8" t="n">
-        <v>2.134446416845715</v>
+        <v>2.134</v>
       </c>
       <c r="H8" t="n">
-        <v>187.485347</v>
+        <v>187.49</v>
       </c>
       <c r="I8" t="n">
-        <v>87.61493039019865</v>
+        <v>87.61499999999999</v>
       </c>
       <c r="J8" t="inlineStr"/>
     </row>
@@ -723,16 +723,16 @@
         <v>3938370</v>
       </c>
       <c r="F9" t="n">
-        <v>3.93837</v>
+        <v>3.94</v>
       </c>
       <c r="G9" t="n">
-        <v>1.840463902498187</v>
+        <v>1.84</v>
       </c>
       <c r="H9" t="n">
-        <v>191.423717</v>
+        <v>191.42</v>
       </c>
       <c r="I9" t="n">
-        <v>89.45539429269684</v>
+        <v>89.455</v>
       </c>
       <c r="J9" t="inlineStr"/>
     </row>
@@ -755,16 +755,16 @@
         <v>3110345</v>
       </c>
       <c r="F10" t="n">
-        <v>3.110345</v>
+        <v>3.11</v>
       </c>
       <c r="G10" t="n">
-        <v>1.453514448062453</v>
+        <v>1.454</v>
       </c>
       <c r="H10" t="n">
-        <v>194.534062</v>
+        <v>194.53</v>
       </c>
       <c r="I10" t="n">
-        <v>90.9089087407593</v>
+        <v>90.90900000000001</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -791,16 +791,16 @@
         <v>2897121</v>
       </c>
       <c r="F11" t="n">
-        <v>2.897121</v>
+        <v>2.9</v>
       </c>
       <c r="G11" t="n">
-        <v>1.353871429466873</v>
+        <v>1.354</v>
       </c>
       <c r="H11" t="n">
-        <v>197.431183</v>
+        <v>197.43</v>
       </c>
       <c r="I11" t="n">
-        <v>92.26278017022616</v>
+        <v>92.26300000000001</v>
       </c>
       <c r="J11" t="inlineStr"/>
     </row>
@@ -823,16 +823,16 @@
         <v>2344151</v>
       </c>
       <c r="F12" t="n">
-        <v>2.344151</v>
+        <v>2.34</v>
       </c>
       <c r="G12" t="n">
-        <v>1.095459618447486</v>
+        <v>1.095</v>
       </c>
       <c r="H12" t="n">
-        <v>199.775334</v>
+        <v>199.78</v>
       </c>
       <c r="I12" t="n">
-        <v>93.35823978867366</v>
+        <v>93.358</v>
       </c>
       <c r="J12" t="inlineStr"/>
     </row>
@@ -855,16 +855,16 @@
         <v>2164847</v>
       </c>
       <c r="F13" t="n">
-        <v>2.164847</v>
+        <v>2.16</v>
       </c>
       <c r="G13" t="n">
-        <v>1.011667963632541</v>
+        <v>1.012</v>
       </c>
       <c r="H13" t="n">
-        <v>201.940181</v>
+        <v>201.94</v>
       </c>
       <c r="I13" t="n">
-        <v>94.36990775230619</v>
+        <v>94.37</v>
       </c>
       <c r="J13" t="inlineStr"/>
     </row>
@@ -887,16 +887,16 @@
         <v>2024459</v>
       </c>
       <c r="F14" t="n">
-        <v>2.024459</v>
+        <v>2.02</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9460623840796005</v>
+        <v>0.946</v>
       </c>
       <c r="H14" t="n">
-        <v>203.96464</v>
+        <v>203.96</v>
       </c>
       <c r="I14" t="n">
-        <v>95.3159701363858</v>
+        <v>95.316</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>1213314</v>
       </c>
       <c r="F15" t="n">
-        <v>1.213314</v>
+        <v>1.21</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5670012262422487</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>205.177954</v>
+        <v>205.18</v>
       </c>
       <c r="I15" t="n">
-        <v>95.88297136262804</v>
+        <v>95.883</v>
       </c>
       <c r="J15" t="inlineStr"/>
     </row>
@@ -955,16 +955,16 @@
         <v>995516</v>
       </c>
       <c r="F16" t="n">
-        <v>0.995516</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.465220703580259</v>
+        <v>0.465</v>
       </c>
       <c r="H16" t="n">
-        <v>206.17347</v>
+        <v>206.17</v>
       </c>
       <c r="I16" t="n">
-        <v>96.3481920662083</v>
+        <v>96.348</v>
       </c>
       <c r="J16" t="inlineStr"/>
     </row>
@@ -987,16 +987,16 @@
         <v>864126</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8641259999999999</v>
+        <v>0.86</v>
       </c>
       <c r="G17" t="n">
-        <v>0.403820034737759</v>
+        <v>0.404</v>
       </c>
       <c r="H17" t="n">
-        <v>207.037596</v>
+        <v>207.04</v>
       </c>
       <c r="I17" t="n">
-        <v>96.75201210094606</v>
+        <v>96.752</v>
       </c>
       <c r="J17" t="inlineStr"/>
     </row>
@@ -1019,16 +1019,16 @@
         <v>863936</v>
       </c>
       <c r="F18" t="n">
-        <v>0.863936</v>
+        <v>0.86</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4037312446694123</v>
+        <v>0.404</v>
       </c>
       <c r="H18" t="n">
-        <v>207.901532</v>
+        <v>207.9</v>
       </c>
       <c r="I18" t="n">
-        <v>97.15574334561548</v>
+        <v>97.15600000000001</v>
       </c>
       <c r="J18" t="inlineStr"/>
     </row>
@@ -1051,16 +1051,16 @@
         <v>678714</v>
       </c>
       <c r="F19" t="n">
-        <v>0.678714</v>
+        <v>0.68</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3171740128835417</v>
+        <v>0.317</v>
       </c>
       <c r="H19" t="n">
-        <v>208.580246</v>
+        <v>208.58</v>
       </c>
       <c r="I19" t="n">
-        <v>97.47291735849902</v>
+        <v>97.473</v>
       </c>
       <c r="J19" t="inlineStr"/>
     </row>
@@ -1083,16 +1083,16 @@
         <v>569087</v>
       </c>
       <c r="F20" t="n">
-        <v>0.569087</v>
+        <v>0.57</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2659435453959342</v>
+        <v>0.266</v>
       </c>
       <c r="H20" t="n">
-        <v>209.149333</v>
+        <v>209.15</v>
       </c>
       <c r="I20" t="n">
-        <v>97.73886090389496</v>
+        <v>97.739</v>
       </c>
       <c r="J20" t="inlineStr"/>
     </row>
@@ -1115,16 +1115,16 @@
         <v>491136</v>
       </c>
       <c r="F21" t="n">
-        <v>0.491136</v>
+        <v>0.49</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2295157842501719</v>
+        <v>0.23</v>
       </c>
       <c r="H21" t="n">
-        <v>209.640469</v>
+        <v>209.64</v>
       </c>
       <c r="I21" t="n">
-        <v>97.96837668814511</v>
+        <v>97.968</v>
       </c>
       <c r="J21" t="inlineStr"/>
     </row>
@@ -1147,16 +1147,16 @@
         <v>482869</v>
       </c>
       <c r="F22" t="n">
-        <v>0.482869</v>
+        <v>0.48</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2256524816447913</v>
+        <v>0.226</v>
       </c>
       <c r="H22" t="n">
-        <v>210.123338</v>
+        <v>210.12</v>
       </c>
       <c r="I22" t="n">
-        <v>98.19402916978991</v>
+        <v>98.194</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1183,16 +1183,16 @@
         <v>450989</v>
       </c>
       <c r="F23" t="n">
-        <v>0.450989</v>
+        <v>0.45</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2107544428085108</v>
+        <v>0.211</v>
       </c>
       <c r="H23" t="n">
-        <v>210.574327</v>
+        <v>210.57</v>
       </c>
       <c r="I23" t="n">
-        <v>98.40478361259842</v>
+        <v>98.405</v>
       </c>
       <c r="J23" t="inlineStr"/>
     </row>
@@ -1215,16 +1215,16 @@
         <v>443024</v>
       </c>
       <c r="F24" t="n">
-        <v>0.443024</v>
+        <v>0.44</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2070322696801866</v>
+        <v>0.207</v>
       </c>
       <c r="H24" t="n">
-        <v>211.017351</v>
+        <v>211.02</v>
       </c>
       <c r="I24" t="n">
-        <v>98.61181588227861</v>
+        <v>98.61199999999999</v>
       </c>
       <c r="J24" t="inlineStr"/>
     </row>
@@ -1247,16 +1247,16 @@
         <v>338210</v>
       </c>
       <c r="F25" t="n">
-        <v>0.33821</v>
+        <v>0.34</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1580509948186462</v>
+        <v>0.158</v>
       </c>
       <c r="H25" t="n">
-        <v>211.355561</v>
+        <v>211.36</v>
       </c>
       <c r="I25" t="n">
-        <v>98.76986687709726</v>
+        <v>98.77</v>
       </c>
       <c r="J25" t="inlineStr"/>
     </row>
@@ -1279,16 +1279,16 @@
         <v>328217</v>
       </c>
       <c r="F26" t="n">
-        <v>0.328217</v>
+        <v>0.33</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1533811045397581</v>
+        <v>0.153</v>
       </c>
       <c r="H26" t="n">
-        <v>211.683778</v>
+        <v>211.68</v>
       </c>
       <c r="I26" t="n">
-        <v>98.92324798163702</v>
+        <v>98.923</v>
       </c>
       <c r="J26" t="inlineStr"/>
     </row>
@@ -1311,16 +1311,16 @@
         <v>225830</v>
       </c>
       <c r="F27" t="n">
-        <v>0.22583</v>
+        <v>0.23</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1055340059723097</v>
+        <v>0.106</v>
       </c>
       <c r="H27" t="n">
-        <v>211.909608</v>
+        <v>211.91</v>
       </c>
       <c r="I27" t="n">
-        <v>99.02878198760932</v>
+        <v>99.029</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>173739</v>
       </c>
       <c r="F28" t="n">
-        <v>0.173739</v>
+        <v>0.17</v>
       </c>
       <c r="G28" t="n">
-        <v>0.08119104044468459</v>
+        <v>0.081</v>
       </c>
       <c r="H28" t="n">
-        <v>212.083347</v>
+        <v>212.08</v>
       </c>
       <c r="I28" t="n">
-        <v>99.10997302805401</v>
+        <v>99.11</v>
       </c>
       <c r="J28" t="inlineStr"/>
     </row>
@@ -1379,16 +1379,16 @@
         <v>172286</v>
       </c>
       <c r="F29" t="n">
-        <v>0.172286</v>
+        <v>0.17</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0805120300799068</v>
+        <v>0.081</v>
       </c>
       <c r="H29" t="n">
-        <v>212.255633</v>
+        <v>212.26</v>
       </c>
       <c r="I29" t="n">
-        <v>99.19048505813392</v>
+        <v>99.19</v>
       </c>
       <c r="J29" t="inlineStr"/>
     </row>
@@ -1411,16 +1411,16 @@
         <v>156706</v>
       </c>
       <c r="F30" t="n">
-        <v>0.156706</v>
+        <v>0.16</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0732312444754761</v>
+        <v>0.073</v>
       </c>
       <c r="H30" t="n">
-        <v>212.412339</v>
+        <v>212.41</v>
       </c>
       <c r="I30" t="n">
-        <v>99.2637163026094</v>
+        <v>99.264</v>
       </c>
       <c r="J30" t="inlineStr"/>
     </row>
@@ -1443,16 +1443,16 @@
         <v>155970</v>
       </c>
       <c r="F31" t="n">
-        <v>0.15597</v>
+        <v>0.16</v>
       </c>
       <c r="G31" t="n">
-        <v>0.07288729978966989</v>
+        <v>0.073</v>
       </c>
       <c r="H31" t="n">
-        <v>212.568309</v>
+        <v>212.57</v>
       </c>
       <c r="I31" t="n">
-        <v>99.33660360239907</v>
+        <v>99.337</v>
       </c>
       <c r="J31" t="inlineStr"/>
     </row>
@@ -1475,16 +1475,16 @@
         <v>154337</v>
       </c>
       <c r="F32" t="n">
-        <v>0.154337</v>
+        <v>0.15</v>
       </c>
       <c r="G32" t="n">
-        <v>0.07212417251803732</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>212.722646</v>
+        <v>212.72</v>
       </c>
       <c r="I32" t="n">
-        <v>99.40872777491711</v>
+        <v>99.40900000000001</v>
       </c>
       <c r="J32" t="inlineStr"/>
     </row>
@@ -1507,16 +1507,16 @@
         <v>152760</v>
       </c>
       <c r="F33" t="n">
-        <v>0.15276</v>
+        <v>0.15</v>
       </c>
       <c r="G33" t="n">
-        <v>0.07138721495075957</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>212.875406</v>
+        <v>212.88</v>
       </c>
       <c r="I33" t="n">
-        <v>99.48011498986786</v>
+        <v>99.48</v>
       </c>
       <c r="J33" t="inlineStr"/>
     </row>
@@ -1539,16 +1539,16 @@
         <v>136521</v>
       </c>
       <c r="F34" t="n">
-        <v>0.136521</v>
+        <v>0.14</v>
       </c>
       <c r="G34" t="n">
-        <v>0.06379846800401053</v>
+        <v>0.064</v>
       </c>
       <c r="H34" t="n">
-        <v>213.011927</v>
+        <v>213.01</v>
       </c>
       <c r="I34" t="n">
-        <v>99.54391345787187</v>
+        <v>99.544</v>
       </c>
       <c r="J34" t="inlineStr"/>
     </row>
@@ -1571,16 +1571,16 @@
         <v>119614</v>
       </c>
       <c r="F35" t="n">
-        <v>0.119614</v>
+        <v>0.12</v>
       </c>
       <c r="G35" t="n">
-        <v>0.05589755386960039</v>
+        <v>0.056</v>
       </c>
       <c r="H35" t="n">
-        <v>213.131541</v>
+        <v>213.13</v>
       </c>
       <c r="I35" t="n">
-        <v>99.59981101174147</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="J35" t="inlineStr"/>
     </row>
@@ -1603,16 +1603,16 @@
         <v>109977</v>
       </c>
       <c r="F36" t="n">
-        <v>0.109977</v>
+        <v>0.11</v>
       </c>
       <c r="G36" t="n">
-        <v>0.05139402813982513</v>
+        <v>0.051</v>
       </c>
       <c r="H36" t="n">
-        <v>213.241518</v>
+        <v>213.24</v>
       </c>
       <c r="I36" t="n">
-        <v>99.65120503988129</v>
+        <v>99.651</v>
       </c>
       <c r="J36" t="inlineStr"/>
     </row>
@@ -1635,16 +1635,16 @@
         <v>107341</v>
       </c>
       <c r="F37" t="n">
-        <v>0.107341</v>
+        <v>0.11</v>
       </c>
       <c r="G37" t="n">
-        <v>0.05016218277055173</v>
+        <v>0.05</v>
       </c>
       <c r="H37" t="n">
-        <v>213.348859</v>
+        <v>213.35</v>
       </c>
       <c r="I37" t="n">
-        <v>99.70136722265185</v>
+        <v>99.70099999999999</v>
       </c>
       <c r="J37" t="inlineStr"/>
     </row>
@@ -1667,16 +1667,16 @@
         <v>101196</v>
       </c>
       <c r="F38" t="n">
-        <v>0.101196</v>
+        <v>0.1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.04729052503375927</v>
+        <v>0.047</v>
       </c>
       <c r="H38" t="n">
-        <v>213.450055</v>
+        <v>213.45</v>
       </c>
       <c r="I38" t="n">
-        <v>99.74865774768561</v>
+        <v>99.749</v>
       </c>
       <c r="J38" t="inlineStr"/>
     </row>
@@ -1699,16 +1699,16 @@
         <v>83990</v>
       </c>
       <c r="F39" t="n">
-        <v>0.08399</v>
+        <v>0.08</v>
       </c>
       <c r="G39" t="n">
-        <v>0.03924988337074035</v>
+        <v>0.039</v>
       </c>
       <c r="H39" t="n">
-        <v>213.534045</v>
+        <v>213.53</v>
       </c>
       <c r="I39" t="n">
-        <v>99.78790763105636</v>
+        <v>99.788</v>
       </c>
       <c r="J39" t="inlineStr"/>
     </row>
@@ -1731,16 +1731,16 @@
         <v>79733</v>
       </c>
       <c r="F40" t="n">
-        <v>0.079733</v>
+        <v>0.08</v>
       </c>
       <c r="G40" t="n">
-        <v>0.03726051852362473</v>
+        <v>0.037</v>
       </c>
       <c r="H40" t="n">
-        <v>213.613778</v>
+        <v>213.61</v>
       </c>
       <c r="I40" t="n">
-        <v>99.82516814957998</v>
+        <v>99.825</v>
       </c>
       <c r="J40" t="inlineStr"/>
     </row>
@@ -1763,16 +1763,16 @@
         <v>68468</v>
       </c>
       <c r="F41" t="n">
-        <v>0.068468</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>0.03199620210296286</v>
+        <v>0.032</v>
       </c>
       <c r="H41" t="n">
-        <v>213.682246</v>
+        <v>213.68</v>
       </c>
       <c r="I41" t="n">
-        <v>99.85716435168294</v>
+        <v>99.857</v>
       </c>
       <c r="J41" t="inlineStr"/>
     </row>
@@ -1795,16 +1795,16 @@
         <v>68300</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0683</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0319176929898984</v>
+        <v>0.032</v>
       </c>
       <c r="H42" t="n">
-        <v>213.750546</v>
+        <v>213.75</v>
       </c>
       <c r="I42" t="n">
-        <v>99.88908204467283</v>
+        <v>99.889</v>
       </c>
       <c r="J42" t="inlineStr"/>
     </row>
@@ -1827,16 +1827,16 @@
         <v>63240</v>
       </c>
       <c r="F43" t="n">
-        <v>0.06324</v>
+        <v>0.06</v>
       </c>
       <c r="G43" t="n">
-        <v>0.02955307327498059</v>
+        <v>0.03</v>
       </c>
       <c r="H43" t="n">
-        <v>213.813786</v>
+        <v>213.81</v>
       </c>
       <c r="I43" t="n">
-        <v>99.91863511794782</v>
+        <v>99.919</v>
       </c>
       <c r="J43" t="inlineStr"/>
     </row>
@@ -1859,16 +1859,16 @@
         <v>46065</v>
       </c>
       <c r="F44" t="n">
-        <v>0.046065</v>
+        <v>0.05</v>
       </c>
       <c r="G44" t="n">
-        <v>0.02152691841258667</v>
+        <v>0.022</v>
       </c>
       <c r="H44" t="n">
-        <v>213.859851</v>
+        <v>213.86</v>
       </c>
       <c r="I44" t="n">
-        <v>99.94016203636041</v>
+        <v>99.94</v>
       </c>
       <c r="J44" t="inlineStr"/>
     </row>
@@ -1891,16 +1891,16 @@
         <v>32191</v>
       </c>
       <c r="F45" t="n">
-        <v>0.032191</v>
+        <v>0.03</v>
       </c>
       <c r="G45" t="n">
-        <v>0.01504337415867964</v>
+        <v>0.015</v>
       </c>
       <c r="H45" t="n">
-        <v>213.892042</v>
+        <v>213.89</v>
       </c>
       <c r="I45" t="n">
-        <v>99.95520541051907</v>
+        <v>99.955</v>
       </c>
       <c r="J45" t="inlineStr"/>
     </row>
@@ -1923,16 +1923,16 @@
         <v>28534</v>
       </c>
       <c r="F46" t="n">
-        <v>0.028534</v>
+        <v>0.03</v>
       </c>
       <c r="G46" t="n">
-        <v>0.01333439900107995</v>
+        <v>0.013</v>
       </c>
       <c r="H46" t="n">
-        <v>213.920576</v>
+        <v>213.92</v>
       </c>
       <c r="I46" t="n">
-        <v>99.96853980952017</v>
+        <v>99.96899999999999</v>
       </c>
       <c r="J46" t="inlineStr"/>
     </row>
@@ -1955,16 +1955,16 @@
         <v>21568</v>
       </c>
       <c r="F47" t="n">
-        <v>0.021568</v>
+        <v>0.02</v>
       </c>
       <c r="G47" t="n">
-        <v>0.01007907470579983</v>
+        <v>0.01</v>
       </c>
       <c r="H47" t="n">
-        <v>213.942144</v>
+        <v>213.94</v>
       </c>
       <c r="I47" t="n">
-        <v>99.97861888422597</v>
+        <v>99.979</v>
       </c>
       <c r="J47" t="inlineStr"/>
     </row>
@@ -1987,16 +1987,16 @@
         <v>19562</v>
       </c>
       <c r="F48" t="n">
-        <v>0.019562</v>
+        <v>0.02</v>
       </c>
       <c r="G48" t="n">
-        <v>0.009141638510518191</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>213.961706</v>
+        <v>213.96</v>
       </c>
       <c r="I48" t="n">
-        <v>99.98776052273648</v>
+        <v>99.988</v>
       </c>
       <c r="J48" t="inlineStr"/>
     </row>
@@ -2019,16 +2019,16 @@
         <v>11837</v>
       </c>
       <c r="F49" t="n">
-        <v>0.011837</v>
+        <v>0.01</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0055316212580004</v>
+        <v>0.006</v>
       </c>
       <c r="H49" t="n">
-        <v>213.973543</v>
+        <v>213.97</v>
       </c>
       <c r="I49" t="n">
-        <v>99.99329214399448</v>
+        <v>99.99299999999999</v>
       </c>
       <c r="J49" t="inlineStr"/>
     </row>
@@ -2051,16 +2051,16 @@
         <v>9409</v>
       </c>
       <c r="F50" t="n">
-        <v>0.009409000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="G50" t="n">
-        <v>0.00439697764775921</v>
+        <v>0.004</v>
       </c>
       <c r="H50" t="n">
-        <v>213.982952</v>
+        <v>213.98</v>
       </c>
       <c r="I50" t="n">
-        <v>99.99768912164224</v>
+        <v>99.998</v>
       </c>
       <c r="J50" t="inlineStr"/>
     </row>
@@ -2083,16 +2083,16 @@
         <v>4719</v>
       </c>
       <c r="F51" t="n">
-        <v>0.004719</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.002205264908042907</v>
+        <v>0.002</v>
       </c>
       <c r="H51" t="n">
-        <v>213.987671</v>
+        <v>213.99</v>
       </c>
       <c r="I51" t="n">
-        <v>99.99989438655028</v>
+        <v>100</v>
       </c>
       <c r="J51" t="inlineStr"/>
     </row>
@@ -2115,13 +2115,13 @@
         <v>226</v>
       </c>
       <c r="F52" t="n">
-        <v>0.000226</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0001056134497176726</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>213.987897</v>
+        <v>213.99</v>
       </c>
       <c r="I52" t="n">
         <v>100</v>
